--- a/data/Les Terrasses de Gallieni.xlsx
+++ b/data/Les Terrasses de Gallieni.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Modélisation de la copropriété/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="266" documentId="13_ncr:1_{BC6B5EAF-A22B-4219-B771-90D3DDB91BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4959D8B7-059E-45D7-8A9D-814E9D9AC1F9}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="13_ncr:1_{BC6B5EAF-A22B-4219-B771-90D3DDB91BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{681B539C-AB20-4DB7-84CF-ABF379C2454E}"/>
   <bookViews>
-    <workbookView xWindow="3525" yWindow="4590" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3870" yWindow="4935" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenus" sheetId="3" r:id="rId1"/>
@@ -63,9 +63,6 @@
     <t>TTC</t>
   </si>
   <si>
-    <t>Victor DINE</t>
-  </si>
-  <si>
     <t>Total TTC</t>
   </si>
   <si>
@@ -737,7 +734,10 @@
     <t>Lot 308 - T2 2ème étage Batiment 3 exposé ouest</t>
   </si>
   <si>
-    <t>Sandrine MATTIUZ</t>
+    <t>Lot 134</t>
+  </si>
+  <si>
+    <t>Lot 113</t>
   </si>
 </sst>
 </file>
@@ -1559,7 +1559,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1598,33 +1598,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" t="s">
         <v>114</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>115</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E2" s="1">
         <v>1500</v>
@@ -1632,16 +1632,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E3" s="1">
         <v>1500</v>
@@ -1649,16 +1649,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" s="1">
         <v>2000</v>
@@ -1666,16 +1666,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E5" s="1">
         <v>2900</v>
@@ -1683,16 +1683,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="1">
         <v>1000</v>
@@ -1700,16 +1700,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E7" s="1">
         <v>2900</v>
@@ -1717,16 +1717,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1">
         <v>1000</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" s="1">
         <v>750</v>
@@ -1751,16 +1751,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="1">
         <v>6200</v>
@@ -1768,16 +1768,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" s="1">
         <v>1050</v>
@@ -1785,16 +1785,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" s="1">
         <v>900</v>
@@ -1802,16 +1802,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" s="1">
         <v>920</v>
@@ -1819,16 +1819,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" s="1">
         <v>35000</v>
@@ -1836,16 +1836,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" s="1">
         <v>1500</v>
@@ -1853,16 +1853,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E16" s="1">
         <v>580</v>
@@ -1870,16 +1870,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" s="1">
         <v>570</v>
@@ -1887,16 +1887,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" s="1">
         <v>850</v>
@@ -1904,16 +1904,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" s="1">
         <v>240</v>
@@ -1921,16 +1921,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20" s="1">
         <v>220</v>
@@ -1938,16 +1938,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E21" s="1">
         <v>18000</v>
@@ -1955,31 +1955,31 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E22" s="1"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" s="1">
         <v>650</v>
@@ -1987,16 +1987,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E24" s="1">
         <v>3500</v>
@@ -2004,16 +2004,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E25" s="1">
         <v>16800</v>
@@ -2021,16 +2021,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" t="s">
         <v>96</v>
       </c>
-      <c r="B26" t="s">
-        <v>219</v>
-      </c>
-      <c r="C26" t="s">
-        <v>97</v>
-      </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E26" s="1">
         <v>4000</v>
@@ -2038,16 +2038,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" s="1">
         <v>23100</v>
@@ -2055,16 +2055,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" s="1">
         <v>27000</v>
@@ -2072,16 +2072,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" s="1">
         <v>17650</v>
@@ -2089,16 +2089,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30" s="1">
         <v>90</v>
@@ -2106,16 +2106,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" t="s">
         <v>65</v>
       </c>
-      <c r="C31" t="s">
-        <v>66</v>
-      </c>
       <c r="D31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" s="1">
         <v>450</v>
@@ -2123,16 +2123,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E32" s="1">
         <v>320</v>
@@ -2140,16 +2140,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E33" s="1">
         <v>1500</v>
@@ -2157,16 +2157,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E34" s="1">
         <v>360</v>
@@ -2207,39 +2207,39 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" t="s">
         <v>111</v>
       </c>
-      <c r="D1" t="s">
-        <v>112</v>
-      </c>
       <c r="E1" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
         <v>29</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>6</v>
@@ -2249,21 +2249,21 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E3" s="6">
         <v>0</v>
@@ -2276,21 +2276,21 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E4" s="6">
         <v>10000</v>
@@ -2303,21 +2303,21 @@
         <v>10000</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
         <v>201</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>202</v>
       </c>
       <c r="E5" s="6">
         <v>16000</v>
@@ -2330,21 +2330,21 @@
         <v>16000</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E6" s="6">
         <v>1940</v>
@@ -2357,21 +2357,21 @@
         <v>1940</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E7" s="6">
         <v>18000</v>
@@ -2384,21 +2384,21 @@
         <v>18000</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
         <v>201</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>202</v>
       </c>
       <c r="E8" s="6">
         <v>24000</v>
@@ -2411,21 +2411,21 @@
         <v>24000</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E9" s="6">
         <v>5710</v>
@@ -2438,21 +2438,21 @@
         <v>5710</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E10" s="6">
         <v>20000</v>
@@ -2465,21 +2465,21 @@
         <v>20000</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
         <v>201</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" t="s">
-        <v>202</v>
       </c>
       <c r="E11" s="6">
         <v>37000</v>
@@ -2492,21 +2492,21 @@
         <v>37000</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E12" s="6">
         <v>10770</v>
@@ -2519,21 +2519,21 @@
         <v>10770</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E13" s="6">
         <v>25000</v>
@@ -2546,18 +2546,18 @@
         <v>25000</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" t="s">
         <v>15</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
       </c>
       <c r="E14" s="6">
         <v>3000</v>
@@ -2572,13 +2572,13 @@
     </row>
     <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" s="6">
         <v>2460</v>
@@ -2593,16 +2593,16 @@
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" s="6">
         <v>1051.2</v>
@@ -2615,21 +2615,21 @@
         <v>1051.2</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E17" s="6">
         <v>748.15</v>
@@ -2642,21 +2642,21 @@
         <v>748.15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" t="s">
         <v>11</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
       </c>
       <c r="E18" s="6">
         <v>6096.65</v>
@@ -2669,21 +2669,21 @@
         <v>6096.65</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" s="6">
         <v>7502.9</v>
@@ -2696,21 +2696,21 @@
         <v>7502.9</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E20" s="6">
         <f>16750</f>
@@ -2724,21 +2724,21 @@
         <v>16750</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E21" s="6">
         <f>887</f>
@@ -2752,21 +2752,21 @@
         <v>887</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>6</v>
@@ -2776,21 +2776,21 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" t="s">
         <v>26</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" t="s">
-        <v>27</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>6</v>
@@ -2800,21 +2800,21 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E24" s="6">
         <f>1140*12</f>
@@ -2828,21 +2828,21 @@
         <v>13680</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E25" s="6">
         <f>2836.8*12</f>
@@ -2856,21 +2856,21 @@
         <v>34041.600000000006</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E26" s="6">
         <f>1518*12</f>
@@ -2884,21 +2884,21 @@
         <v>18216</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E27" s="6">
         <v>516</v>
@@ -2911,21 +2911,21 @@
         <v>516</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E28" s="6">
         <v>456</v>
@@ -2938,21 +2938,21 @@
         <v>456</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" t="s">
         <v>24</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C29" t="s">
-        <v>92</v>
-      </c>
-      <c r="D29" t="s">
-        <v>25</v>
       </c>
       <c r="E29" s="6">
         <v>660</v>
@@ -2965,21 +2965,21 @@
         <v>660</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E30" s="6">
         <v>2400</v>
@@ -2992,21 +2992,21 @@
         <v>2880</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E31" s="6">
         <v>2400</v>
@@ -3019,21 +3019,21 @@
         <v>2880</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E32" s="6">
         <v>2450</v>
@@ -3046,21 +3046,21 @@
         <v>2940</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E33" s="6">
         <v>2200</v>
@@ -3073,18 +3073,18 @@
         <v>2640</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" t="s">
         <v>31</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" t="s">
-        <v>32</v>
       </c>
       <c r="E34" s="6">
         <v>160</v>
@@ -3099,16 +3099,16 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E35" s="6">
         <f>2400*12</f>
@@ -3122,21 +3122,21 @@
         <v>28800</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E36" s="6">
         <f>1320*12</f>
@@ -3150,18 +3150,18 @@
         <v>15840</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E37" s="6">
         <v>3198.13</v>
@@ -3176,13 +3176,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E38" s="6">
         <v>3322.8</v>
@@ -3197,13 +3197,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" t="s">
         <v>20</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D39" t="s">
-        <v>21</v>
       </c>
       <c r="E39" s="6">
         <v>3138.27</v>
@@ -3218,16 +3218,16 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E40" s="6">
         <v>240</v>
@@ -3240,21 +3240,21 @@
         <v>288</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E41" s="6">
         <v>240</v>
@@ -3267,21 +3267,21 @@
         <v>288</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E42" s="6">
         <v>240</v>
@@ -3294,21 +3294,21 @@
         <v>288</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E43" s="6">
         <v>240</v>
@@ -3321,21 +3321,21 @@
         <v>288</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E44" s="7">
         <v>10000</v>
@@ -3352,16 +3352,16 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E45" s="7">
         <v>12500</v>
@@ -3378,16 +3378,16 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D46" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E46" s="7">
         <v>15000</v>
@@ -3404,16 +3404,16 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E47" s="7">
         <v>16800</v>
@@ -3426,7 +3426,7 @@
         <v>16800</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I47" s="2"/>
     </row>
@@ -3476,75 +3476,75 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="E1" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="R1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="I1" s="10" t="s">
+      <c r="S1" t="s">
         <v>180</v>
       </c>
-      <c r="J1" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="S1" t="s">
-        <v>181</v>
-      </c>
       <c r="T1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D2" s="10">
         <v>217</v>
@@ -3581,13 +3581,13 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D3" s="10">
         <v>82</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D4" s="10">
         <v>102</v>
@@ -3668,13 +3668,13 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D5" s="10">
         <v>7</v>
@@ -3710,13 +3710,13 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>231</v>
       </c>
       <c r="D6" s="10">
         <v>86</v>
@@ -3756,13 +3756,13 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>231</v>
       </c>
       <c r="D7" s="10">
         <v>7</v>
@@ -3820,16 +3820,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1">
         <v>-5000</v>
@@ -3879,7 +3879,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1">
         <f>IF(BdRegles[[#This Row],[Taxes]]="HT",BdRegles[[#This Row],[Limite]]*1.2,BdRegles[[#This Row],[Limite]])</f>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1">
         <f>IF(BdRegles[[#This Row],[Taxes]]="HT",BdRegles[[#This Row],[Limite]]*1.2,BdRegles[[#This Row],[Limite]])</f>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1">
         <f>IF(BdRegles[[#This Row],[Taxes]]="HT",BdRegles[[#This Row],[Limite]]*1.2,BdRegles[[#This Row],[Limite]])</f>
@@ -3906,7 +3906,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1">
         <f>IF(BdRegles[[#This Row],[Taxes]]="HT",BdRegles[[#This Row],[Limite]]*1.2,BdRegles[[#This Row],[Limite]])</f>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1">
         <f>IF(BdRegles[[#This Row],[Taxes]]="HT",BdRegles[[#This Row],[Limite]]*1.2,BdRegles[[#This Row],[Limite]])</f>
